--- a/data/RKLB.xlsx
+++ b/data/RKLB.xlsx
@@ -38210,13 +38210,13 @@
         <v>46276.5625</v>
       </c>
       <c r="B1456" t="n">
-        <v>15238731</v>
+        <v>15335700</v>
       </c>
       <c r="C1456" t="n">
         <v>64.8899993896484</v>
       </c>
       <c r="D1456" t="n">
-        <v>62.0699996948242</v>
+        <v>62.060001373291</v>
       </c>
       <c r="E1456" t="n">
         <v>62.3199996948242</v>
@@ -38228,6 +38228,32 @@
         <v>62.9500007629395</v>
       </c>
       <c r="H1456" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1457">
+      <c r="A1457" s="1" t="n">
+        <v>46279.5625</v>
+      </c>
+      <c r="B1457" t="n">
+        <v>14390623</v>
+      </c>
+      <c r="C1457" t="n">
+        <v>63.375</v>
+      </c>
+      <c r="D1457" t="n">
+        <v>60.5699996948242</v>
+      </c>
+      <c r="E1457" t="n">
+        <v>60.5699996948242</v>
+      </c>
+      <c r="F1457" t="n">
+        <v>62.5499992370605</v>
+      </c>
+      <c r="G1457" t="n">
+        <v>62.5499992370605</v>
+      </c>
+      <c r="H1457" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RKLB.xlsx
+++ b/data/RKLB.xlsx
@@ -38210,7 +38210,7 @@
         <v>46276.5625</v>
       </c>
       <c r="B1456" t="n">
-        <v>15335700</v>
+        <v>15391400</v>
       </c>
       <c r="C1456" t="n">
         <v>64.8899993896484</v>
@@ -38236,16 +38236,16 @@
         <v>46279.5625</v>
       </c>
       <c r="B1457" t="n">
-        <v>14390623</v>
+        <v>14449300</v>
       </c>
       <c r="C1457" t="n">
         <v>63.375</v>
       </c>
       <c r="D1457" t="n">
-        <v>60.5699996948242</v>
+        <v>60.5099983215332</v>
       </c>
       <c r="E1457" t="n">
-        <v>60.5699996948242</v>
+        <v>60.5499992370605</v>
       </c>
       <c r="F1457" t="n">
         <v>62.5499992370605</v>
@@ -38254,6 +38254,32 @@
         <v>62.5499992370605</v>
       </c>
       <c r="H1457" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1458">
+      <c r="A1458" s="1" t="n">
+        <v>46280.5625</v>
+      </c>
+      <c r="B1458" t="n">
+        <v>20269701</v>
+      </c>
+      <c r="C1458" t="n">
+        <v>65.7200012207031</v>
+      </c>
+      <c r="D1458" t="n">
+        <v>62.0200004577637</v>
+      </c>
+      <c r="E1458" t="n">
+        <v>63.6800003051758</v>
+      </c>
+      <c r="F1458" t="n">
+        <v>63.5499992370605</v>
+      </c>
+      <c r="G1458" t="n">
+        <v>63.5499992370605</v>
+      </c>
+      <c r="H1458" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RKLB.xlsx
+++ b/data/RKLB.xlsx
@@ -38262,7 +38262,7 @@
         <v>46280.5625</v>
       </c>
       <c r="B1458" t="n">
-        <v>20269701</v>
+        <v>20448700</v>
       </c>
       <c r="C1458" t="n">
         <v>65.7200012207031</v>
@@ -38280,6 +38280,32 @@
         <v>63.5499992370605</v>
       </c>
       <c r="H1458" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1459">
+      <c r="A1459" s="1" t="n">
+        <v>46281.5625</v>
+      </c>
+      <c r="B1459" t="n">
+        <v>17577566</v>
+      </c>
+      <c r="C1459" t="n">
+        <v>64.55419921875</v>
+      </c>
+      <c r="D1459" t="n">
+        <v>61.7400016784668</v>
+      </c>
+      <c r="E1459" t="n">
+        <v>63.6699981689453</v>
+      </c>
+      <c r="F1459" t="n">
+        <v>63.7000007629395</v>
+      </c>
+      <c r="G1459" t="n">
+        <v>63.7000007629395</v>
+      </c>
+      <c r="H1459" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RKLB.xlsx
+++ b/data/RKLB.xlsx
@@ -38288,10 +38288,10 @@
         <v>46281.5625</v>
       </c>
       <c r="B1459" t="n">
-        <v>17577566</v>
+        <v>17743600</v>
       </c>
       <c r="C1459" t="n">
-        <v>64.55419921875</v>
+        <v>64.5599975585938</v>
       </c>
       <c r="D1459" t="n">
         <v>61.7400016784668</v>
@@ -38306,6 +38306,32 @@
         <v>63.7000007629395</v>
       </c>
       <c r="H1459" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1460">
+      <c r="A1460" s="1" t="n">
+        <v>46282.5625</v>
+      </c>
+      <c r="B1460" t="n">
+        <v>21810895</v>
+      </c>
+      <c r="C1460" t="n">
+        <v>68.3307037353516</v>
+      </c>
+      <c r="D1460" t="n">
+        <v>65.2600021362305</v>
+      </c>
+      <c r="E1460" t="n">
+        <v>65.5500030517578</v>
+      </c>
+      <c r="F1460" t="n">
+        <v>67.8199996948242</v>
+      </c>
+      <c r="G1460" t="n">
+        <v>67.8199996948242</v>
+      </c>
+      <c r="H1460" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RKLB.xlsx
+++ b/data/RKLB.xlsx
@@ -38314,10 +38314,10 @@
         <v>46282.5625</v>
       </c>
       <c r="B1460" t="n">
-        <v>21810895</v>
+        <v>21956000</v>
       </c>
       <c r="C1460" t="n">
-        <v>68.3307037353516</v>
+        <v>68.3310012817383</v>
       </c>
       <c r="D1460" t="n">
         <v>65.2600021362305</v>
@@ -38332,6 +38332,32 @@
         <v>67.8199996948242</v>
       </c>
       <c r="H1460" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1461">
+      <c r="A1461" s="1" t="n">
+        <v>46283.5625</v>
+      </c>
+      <c r="B1461" t="n">
+        <v>31979150</v>
+      </c>
+      <c r="C1461" t="n">
+        <v>68.5999984741211</v>
+      </c>
+      <c r="D1461" t="n">
+        <v>63.7900009155273</v>
+      </c>
+      <c r="E1461" t="n">
+        <v>68.4300003051758</v>
+      </c>
+      <c r="F1461" t="n">
+        <v>64.5699996948242</v>
+      </c>
+      <c r="G1461" t="n">
+        <v>64.5699996948242</v>
+      </c>
+      <c r="H1461" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RKLB.xlsx
+++ b/data/RKLB.xlsx
@@ -38340,10 +38340,10 @@
         <v>46283.5625</v>
       </c>
       <c r="B1461" t="n">
-        <v>31979150</v>
+        <v>32168300</v>
       </c>
       <c r="C1461" t="n">
-        <v>68.5999984741211</v>
+        <v>68.6399993896484</v>
       </c>
       <c r="D1461" t="n">
         <v>63.7900009155273</v>
@@ -38358,6 +38358,32 @@
         <v>64.5699996948242</v>
       </c>
       <c r="H1461" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="A1462" s="1" t="n">
+        <v>46286.5625</v>
+      </c>
+      <c r="B1462" t="n">
+        <v>25434680</v>
+      </c>
+      <c r="C1462" t="n">
+        <v>70.0100021362305</v>
+      </c>
+      <c r="D1462" t="n">
+        <v>65.3399963378906</v>
+      </c>
+      <c r="E1462" t="n">
+        <v>65.4899978637695</v>
+      </c>
+      <c r="F1462" t="n">
+        <v>69.8899993896484</v>
+      </c>
+      <c r="G1462" t="n">
+        <v>69.8899993896484</v>
+      </c>
+      <c r="H1462" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RKLB.xlsx
+++ b/data/RKLB.xlsx
@@ -38340,7 +38340,7 @@
         <v>46283.5625</v>
       </c>
       <c r="B1461" t="n">
-        <v>32168300</v>
+        <v>32298600</v>
       </c>
       <c r="C1461" t="n">
         <v>68.6399993896484</v>
@@ -38366,16 +38366,16 @@
         <v>46286.5625</v>
       </c>
       <c r="B1462" t="n">
-        <v>25434680</v>
+        <v>26038700</v>
       </c>
       <c r="C1462" t="n">
         <v>70.0100021362305</v>
       </c>
       <c r="D1462" t="n">
-        <v>65.3399963378906</v>
+        <v>65.2750015258789</v>
       </c>
       <c r="E1462" t="n">
-        <v>65.4899978637695</v>
+        <v>65.2850036621094</v>
       </c>
       <c r="F1462" t="n">
         <v>69.8899993896484</v>
@@ -38384,6 +38384,32 @@
         <v>69.8899993896484</v>
       </c>
       <c r="H1462" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1463">
+      <c r="A1463" s="1" t="n">
+        <v>46287.5625</v>
+      </c>
+      <c r="B1463" t="n">
+        <v>21927781</v>
+      </c>
+      <c r="C1463" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="D1463" t="n">
+        <v>70.0999984741211</v>
+      </c>
+      <c r="E1463" t="n">
+        <v>71.6449966430664</v>
+      </c>
+      <c r="F1463" t="n">
+        <v>71.9800033569336</v>
+      </c>
+      <c r="G1463" t="n">
+        <v>71.9800033569336</v>
+      </c>
+      <c r="H1463" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RKLB.xlsx
+++ b/data/RKLB.xlsx
@@ -38392,7 +38392,7 @@
         <v>46287.5625</v>
       </c>
       <c r="B1463" t="n">
-        <v>21927781</v>
+        <v>22048800</v>
       </c>
       <c r="C1463" t="n">
         <v>72.5</v>
@@ -38410,6 +38410,32 @@
         <v>71.9800033569336</v>
       </c>
       <c r="H1463" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1464">
+      <c r="A1464" s="1" t="n">
+        <v>46288.5625</v>
+      </c>
+      <c r="B1464" t="n">
+        <v>19110310</v>
+      </c>
+      <c r="C1464" t="n">
+        <v>73.5699996948242</v>
+      </c>
+      <c r="D1464" t="n">
+        <v>70.0800018310547</v>
+      </c>
+      <c r="E1464" t="n">
+        <v>72.8000030517578</v>
+      </c>
+      <c r="F1464" t="n">
+        <v>70.3099975585938</v>
+      </c>
+      <c r="G1464" t="n">
+        <v>70.3099975585938</v>
+      </c>
+      <c r="H1464" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RKLB.xlsx
+++ b/data/RKLB.xlsx
@@ -38418,7 +38418,7 @@
         <v>46288.5625</v>
       </c>
       <c r="B1464" t="n">
-        <v>19110310</v>
+        <v>19258700</v>
       </c>
       <c r="C1464" t="n">
         <v>73.5699996948242</v>
@@ -38427,7 +38427,7 @@
         <v>70.0800018310547</v>
       </c>
       <c r="E1464" t="n">
-        <v>72.8000030517578</v>
+        <v>72.870002746582</v>
       </c>
       <c r="F1464" t="n">
         <v>70.3099975585938</v>
@@ -38436,6 +38436,32 @@
         <v>70.3099975585938</v>
       </c>
       <c r="H1464" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1465">
+      <c r="A1465" s="1" t="n">
+        <v>46289.5625</v>
+      </c>
+      <c r="B1465" t="n">
+        <v>25020442</v>
+      </c>
+      <c r="C1465" t="n">
+        <v>75.4599990844727</v>
+      </c>
+      <c r="D1465" t="n">
+        <v>68.9216003417969</v>
+      </c>
+      <c r="E1465" t="n">
+        <v>69.7750015258789</v>
+      </c>
+      <c r="F1465" t="n">
+        <v>73.6100006103516</v>
+      </c>
+      <c r="G1465" t="n">
+        <v>73.6100006103516</v>
+      </c>
+      <c r="H1465" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RKLB.xlsx
+++ b/data/RKLB.xlsx
@@ -38444,13 +38444,13 @@
         <v>46289.5625</v>
       </c>
       <c r="B1465" t="n">
-        <v>25020442</v>
+        <v>25304900</v>
       </c>
       <c r="C1465" t="n">
         <v>75.4599990844727</v>
       </c>
       <c r="D1465" t="n">
-        <v>68.9216003417969</v>
+        <v>68.9219970703125</v>
       </c>
       <c r="E1465" t="n">
         <v>69.7750015258789</v>
@@ -38462,6 +38462,32 @@
         <v>73.6100006103516</v>
       </c>
       <c r="H1465" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1466">
+      <c r="A1466" s="1" t="n">
+        <v>46290.5625</v>
+      </c>
+      <c r="B1466" t="n">
+        <v>18756601</v>
+      </c>
+      <c r="C1466" t="n">
+        <v>75.3199996948242</v>
+      </c>
+      <c r="D1466" t="n">
+        <v>72.7800979614258</v>
+      </c>
+      <c r="E1466" t="n">
+        <v>74.0999984741211</v>
+      </c>
+      <c r="F1466" t="n">
+        <v>73.9499969482422</v>
+      </c>
+      <c r="G1466" t="n">
+        <v>73.9499969482422</v>
+      </c>
+      <c r="H1466" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RKLB.xlsx
+++ b/data/RKLB.xlsx
@@ -38470,16 +38470,16 @@
         <v>46290.5625</v>
       </c>
       <c r="B1466" t="n">
-        <v>18756601</v>
+        <v>18802600</v>
       </c>
       <c r="C1466" t="n">
         <v>75.3199996948242</v>
       </c>
       <c r="D1466" t="n">
-        <v>72.7800979614258</v>
+        <v>72.7799987792969</v>
       </c>
       <c r="E1466" t="n">
-        <v>74.0999984741211</v>
+        <v>74.1500015258789</v>
       </c>
       <c r="F1466" t="n">
         <v>73.9499969482422</v>
@@ -38488,6 +38488,32 @@
         <v>73.9499969482422</v>
       </c>
       <c r="H1466" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="A1467" s="1" t="n">
+        <v>46293.5625</v>
+      </c>
+      <c r="B1467" t="n">
+        <v>14921349</v>
+      </c>
+      <c r="C1467" t="n">
+        <v>73.7799987792969</v>
+      </c>
+      <c r="D1467" t="n">
+        <v>71.6800003051758</v>
+      </c>
+      <c r="E1467" t="n">
+        <v>73.1999969482422</v>
+      </c>
+      <c r="F1467" t="n">
+        <v>72.1900024414062</v>
+      </c>
+      <c r="G1467" t="n">
+        <v>72.1900024414062</v>
+      </c>
+      <c r="H1467" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RKLB.xlsx
+++ b/data/RKLB.xlsx
@@ -38470,7 +38470,7 @@
         <v>46290.5625</v>
       </c>
       <c r="B1466" t="n">
-        <v>18802600</v>
+        <v>18860400</v>
       </c>
       <c r="C1466" t="n">
         <v>75.3199996948242</v>
@@ -38496,7 +38496,7 @@
         <v>46293.5625</v>
       </c>
       <c r="B1467" t="n">
-        <v>14921349</v>
+        <v>15012400</v>
       </c>
       <c r="C1467" t="n">
         <v>73.7799987792969</v>
@@ -38514,6 +38514,32 @@
         <v>72.1900024414062</v>
       </c>
       <c r="H1467" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="A1468" s="1" t="n">
+        <v>46294.5625</v>
+      </c>
+      <c r="B1468" t="n">
+        <v>18542118</v>
+      </c>
+      <c r="C1468" t="n">
+        <v>74.25</v>
+      </c>
+      <c r="D1468" t="n">
+        <v>69.4000015258789</v>
+      </c>
+      <c r="E1468" t="n">
+        <v>73.4700012207031</v>
+      </c>
+      <c r="F1468" t="n">
+        <v>69.6999969482422</v>
+      </c>
+      <c r="G1468" t="n">
+        <v>69.6999969482422</v>
+      </c>
+      <c r="H1468" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RKLB.xlsx
+++ b/data/RKLB.xlsx
@@ -38522,7 +38522,7 @@
         <v>46294.5625</v>
       </c>
       <c r="B1468" t="n">
-        <v>18542118</v>
+        <v>19684700</v>
       </c>
       <c r="C1468" t="n">
         <v>74.25</v>
@@ -38540,6 +38540,32 @@
         <v>69.6999969482422</v>
       </c>
       <c r="H1468" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="A1469" s="1" t="n">
+        <v>46295.5625</v>
+      </c>
+      <c r="B1469" t="n">
+        <v>21802367</v>
+      </c>
+      <c r="C1469" t="n">
+        <v>74.5749969482422</v>
+      </c>
+      <c r="D1469" t="n">
+        <v>69.629997253418</v>
+      </c>
+      <c r="E1469" t="n">
+        <v>70.629997253418</v>
+      </c>
+      <c r="F1469" t="n">
+        <v>69.6800003051758</v>
+      </c>
+      <c r="G1469" t="n">
+        <v>69.6800003051758</v>
+      </c>
+      <c r="H1469" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RKLB.xlsx
+++ b/data/RKLB.xlsx
@@ -38548,16 +38548,16 @@
         <v>46295.5625</v>
       </c>
       <c r="B1469" t="n">
-        <v>21802367</v>
+        <v>22428600</v>
       </c>
       <c r="C1469" t="n">
-        <v>74.5749969482422</v>
+        <v>74.5800018310547</v>
       </c>
       <c r="D1469" t="n">
         <v>69.629997253418</v>
       </c>
       <c r="E1469" t="n">
-        <v>70.629997253418</v>
+        <v>70.6399993896484</v>
       </c>
       <c r="F1469" t="n">
         <v>69.6800003051758</v>
@@ -38566,6 +38566,32 @@
         <v>69.6800003051758</v>
       </c>
       <c r="H1469" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1470">
+      <c r="A1470" s="1" t="n">
+        <v>46296.5625</v>
+      </c>
+      <c r="B1470" t="n">
+        <v>23171750</v>
+      </c>
+      <c r="C1470" t="n">
+        <v>72.6399993896484</v>
+      </c>
+      <c r="D1470" t="n">
+        <v>69.4300003051758</v>
+      </c>
+      <c r="E1470" t="n">
+        <v>72.0999984741211</v>
+      </c>
+      <c r="F1470" t="n">
+        <v>70.4599990844727</v>
+      </c>
+      <c r="G1470" t="n">
+        <v>70.4599990844727</v>
+      </c>
+      <c r="H1470" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RKLB.xlsx
+++ b/data/RKLB.xlsx
@@ -38574,16 +38574,16 @@
         <v>46296.5625</v>
       </c>
       <c r="B1470" t="n">
-        <v>23171750</v>
+        <v>23312600</v>
       </c>
       <c r="C1470" t="n">
         <v>72.6399993896484</v>
       </c>
       <c r="D1470" t="n">
-        <v>69.4300003051758</v>
+        <v>69.4240036010742</v>
       </c>
       <c r="E1470" t="n">
-        <v>72.0999984741211</v>
+        <v>72.3099975585938</v>
       </c>
       <c r="F1470" t="n">
         <v>70.4599990844727</v>
@@ -38592,6 +38592,32 @@
         <v>70.4599990844727</v>
       </c>
       <c r="H1470" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1471">
+      <c r="A1471" s="1" t="n">
+        <v>46297.5625</v>
+      </c>
+      <c r="B1471" t="n">
+        <v>26690942</v>
+      </c>
+      <c r="C1471" t="n">
+        <v>76.0898971557617</v>
+      </c>
+      <c r="D1471" t="n">
+        <v>71.4499969482422</v>
+      </c>
+      <c r="E1471" t="n">
+        <v>72.1399993896484</v>
+      </c>
+      <c r="F1471" t="n">
+        <v>73.9199981689453</v>
+      </c>
+      <c r="G1471" t="n">
+        <v>73.9199981689453</v>
+      </c>
+      <c r="H1471" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RKLB.xlsx
+++ b/data/RKLB.xlsx
@@ -38600,16 +38600,16 @@
         <v>46297.5625</v>
       </c>
       <c r="B1471" t="n">
-        <v>26690942</v>
+        <v>26741800</v>
       </c>
       <c r="C1471" t="n">
-        <v>76.0898971557617</v>
+        <v>76.0899963378906</v>
       </c>
       <c r="D1471" t="n">
         <v>71.4499969482422</v>
       </c>
       <c r="E1471" t="n">
-        <v>72.1399993896484</v>
+        <v>72.0849990844727</v>
       </c>
       <c r="F1471" t="n">
         <v>73.9199981689453</v>
@@ -38618,6 +38618,32 @@
         <v>73.9199981689453</v>
       </c>
       <c r="H1471" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1472">
+      <c r="A1472" s="1" t="n">
+        <v>46300.5625</v>
+      </c>
+      <c r="B1472" t="n">
+        <v>18979357</v>
+      </c>
+      <c r="C1472" t="n">
+        <v>73.8099975585938</v>
+      </c>
+      <c r="D1472" t="n">
+        <v>71.370002746582</v>
+      </c>
+      <c r="E1472" t="n">
+        <v>73.5899963378906</v>
+      </c>
+      <c r="F1472" t="n">
+        <v>73.0199966430664</v>
+      </c>
+      <c r="G1472" t="n">
+        <v>73.0199966430664</v>
+      </c>
+      <c r="H1472" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RKLB.xlsx
+++ b/data/RKLB.xlsx
@@ -38600,7 +38600,7 @@
         <v>46297.5625</v>
       </c>
       <c r="B1471" t="n">
-        <v>26741800</v>
+        <v>26839300</v>
       </c>
       <c r="C1471" t="n">
         <v>76.0899963378906</v>
@@ -38626,7 +38626,7 @@
         <v>46300.5625</v>
       </c>
       <c r="B1472" t="n">
-        <v>18979357</v>
+        <v>19107800</v>
       </c>
       <c r="C1472" t="n">
         <v>73.8099975585938</v>
@@ -38635,7 +38635,7 @@
         <v>71.370002746582</v>
       </c>
       <c r="E1472" t="n">
-        <v>73.5899963378906</v>
+        <v>73.6999969482422</v>
       </c>
       <c r="F1472" t="n">
         <v>73.0199966430664</v>
@@ -38644,6 +38644,32 @@
         <v>73.0199966430664</v>
       </c>
       <c r="H1472" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1473">
+      <c r="A1473" s="1" t="n">
+        <v>46301.5625</v>
+      </c>
+      <c r="B1473" t="n">
+        <v>26870720</v>
+      </c>
+      <c r="C1473" t="n">
+        <v>78.2799987792969</v>
+      </c>
+      <c r="D1473" t="n">
+        <v>73.6600036621094</v>
+      </c>
+      <c r="E1473" t="n">
+        <v>74.7750015258789</v>
+      </c>
+      <c r="F1473" t="n">
+        <v>75.0599975585938</v>
+      </c>
+      <c r="G1473" t="n">
+        <v>75.0599975585938</v>
+      </c>
+      <c r="H1473" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RKLB.xlsx
+++ b/data/RKLB.xlsx
@@ -38652,7 +38652,7 @@
         <v>46301.5625</v>
       </c>
       <c r="B1473" t="n">
-        <v>26870720</v>
+        <v>27029200</v>
       </c>
       <c r="C1473" t="n">
         <v>78.2799987792969</v>
@@ -38661,7 +38661,7 @@
         <v>73.6600036621094</v>
       </c>
       <c r="E1473" t="n">
-        <v>74.7750015258789</v>
+        <v>74.7600021362305</v>
       </c>
       <c r="F1473" t="n">
         <v>75.0599975585938</v>
@@ -38670,6 +38670,32 @@
         <v>75.0599975585938</v>
       </c>
       <c r="H1473" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="A1474" s="1" t="n">
+        <v>46302.5625</v>
+      </c>
+      <c r="B1474" t="n">
+        <v>20411657</v>
+      </c>
+      <c r="C1474" t="n">
+        <v>73.1500015258789</v>
+      </c>
+      <c r="D1474" t="n">
+        <v>70.629997253418</v>
+      </c>
+      <c r="E1474" t="n">
+        <v>72.9100036621094</v>
+      </c>
+      <c r="F1474" t="n">
+        <v>71.9199981689453</v>
+      </c>
+      <c r="G1474" t="n">
+        <v>71.9199981689453</v>
+      </c>
+      <c r="H1474" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RKLB.xlsx
+++ b/data/RKLB.xlsx
@@ -38678,16 +38678,16 @@
         <v>46302.5625</v>
       </c>
       <c r="B1474" t="n">
-        <v>20411657</v>
+        <v>20500700</v>
       </c>
       <c r="C1474" t="n">
-        <v>73.1500015258789</v>
+        <v>73.1600036621094</v>
       </c>
       <c r="D1474" t="n">
         <v>70.629997253418</v>
       </c>
       <c r="E1474" t="n">
-        <v>72.9100036621094</v>
+        <v>73.1149978637695</v>
       </c>
       <c r="F1474" t="n">
         <v>71.9199981689453</v>
@@ -38696,6 +38696,32 @@
         <v>71.9199981689453</v>
       </c>
       <c r="H1474" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1475">
+      <c r="A1475" s="1" t="n">
+        <v>46303.5625</v>
+      </c>
+      <c r="B1475" t="n">
+        <v>22892581</v>
+      </c>
+      <c r="C1475" t="n">
+        <v>71.6500015258789</v>
+      </c>
+      <c r="D1475" t="n">
+        <v>67.7099990844727</v>
+      </c>
+      <c r="E1475" t="n">
+        <v>70.6050033569336</v>
+      </c>
+      <c r="F1475" t="n">
+        <v>68.4000015258789</v>
+      </c>
+      <c r="G1475" t="n">
+        <v>68.4000015258789</v>
+      </c>
+      <c r="H1475" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RKLB.xlsx
+++ b/data/RKLB.xlsx
@@ -38704,7 +38704,7 @@
         <v>46303.5625</v>
       </c>
       <c r="B1475" t="n">
-        <v>22892581</v>
+        <v>23063500</v>
       </c>
       <c r="C1475" t="n">
         <v>71.6500015258789</v>
@@ -38713,7 +38713,7 @@
         <v>67.7099990844727</v>
       </c>
       <c r="E1475" t="n">
-        <v>70.6050033569336</v>
+        <v>70.5599975585938</v>
       </c>
       <c r="F1475" t="n">
         <v>68.4000015258789</v>
@@ -38722,6 +38722,32 @@
         <v>68.4000015258789</v>
       </c>
       <c r="H1475" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1476">
+      <c r="A1476" s="1" t="n">
+        <v>46304.5625</v>
+      </c>
+      <c r="B1476" t="n">
+        <v>14852656</v>
+      </c>
+      <c r="C1476" t="n">
+        <v>69.245002746582</v>
+      </c>
+      <c r="D1476" t="n">
+        <v>66.9800033569336</v>
+      </c>
+      <c r="E1476" t="n">
+        <v>68.6699981689453</v>
+      </c>
+      <c r="F1476" t="n">
+        <v>68.2099990844727</v>
+      </c>
+      <c r="G1476" t="n">
+        <v>68.2099990844727</v>
+      </c>
+      <c r="H1476" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RKLB.xlsx
+++ b/data/RKLB.xlsx
@@ -38730,16 +38730,16 @@
         <v>46304.5625</v>
       </c>
       <c r="B1476" t="n">
-        <v>14852656</v>
+        <v>14873000</v>
       </c>
       <c r="C1476" t="n">
-        <v>69.245002746582</v>
+        <v>69.25</v>
       </c>
       <c r="D1476" t="n">
         <v>66.9800033569336</v>
       </c>
       <c r="E1476" t="n">
-        <v>68.6699981689453</v>
+        <v>68.7099990844727</v>
       </c>
       <c r="F1476" t="n">
         <v>68.2099990844727</v>

--- a/data/RKLB.xlsx
+++ b/data/RKLB.xlsx
@@ -38782,7 +38782,7 @@
         <v>46308.5625</v>
       </c>
       <c r="B1478" t="n">
-        <v>15510966</v>
+        <v>15588500</v>
       </c>
       <c r="C1478" t="n">
         <v>64.5599975585938</v>
@@ -38791,7 +38791,7 @@
         <v>63.0800018310547</v>
       </c>
       <c r="E1478" t="n">
-        <v>64.0299987792969</v>
+        <v>64.0699996948242</v>
       </c>
       <c r="F1478" t="n">
         <v>64.2200012207031</v>
@@ -38800,6 +38800,32 @@
         <v>64.2200012207031</v>
       </c>
       <c r="H1478" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1479">
+      <c r="A1479" s="1" t="n">
+        <v>46309.5625</v>
+      </c>
+      <c r="B1479" t="n">
+        <v>22490453</v>
+      </c>
+      <c r="C1479" t="n">
+        <v>63.560001373291</v>
+      </c>
+      <c r="D1479" t="n">
+        <v>58.8400001525879</v>
+      </c>
+      <c r="E1479" t="n">
+        <v>62.8349990844727</v>
+      </c>
+      <c r="F1479" t="n">
+        <v>59.1800003051758</v>
+      </c>
+      <c r="G1479" t="n">
+        <v>59.1800003051758</v>
+      </c>
+      <c r="H1479" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RKLB.xlsx
+++ b/data/RKLB.xlsx
@@ -38808,7 +38808,7 @@
         <v>46309.5625</v>
       </c>
       <c r="B1479" t="n">
-        <v>22490453</v>
+        <v>25309100</v>
       </c>
       <c r="C1479" t="n">
         <v>63.560001373291</v>
@@ -38817,7 +38817,7 @@
         <v>58.8400001525879</v>
       </c>
       <c r="E1479" t="n">
-        <v>62.8349990844727</v>
+        <v>62.810001373291</v>
       </c>
       <c r="F1479" t="n">
         <v>59.1800003051758</v>
@@ -38826,6 +38826,32 @@
         <v>59.1800003051758</v>
       </c>
       <c r="H1479" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1480">
+      <c r="A1480" s="1" t="n">
+        <v>46310.5625</v>
+      </c>
+      <c r="B1480" t="n">
+        <v>48106607</v>
+      </c>
+      <c r="C1480" t="n">
+        <v>55.3979988098145</v>
+      </c>
+      <c r="D1480" t="n">
+        <v>49.693000793457</v>
+      </c>
+      <c r="E1480" t="n">
+        <v>54</v>
+      </c>
+      <c r="F1480" t="n">
+        <v>55.25</v>
+      </c>
+      <c r="G1480" t="n">
+        <v>55.25</v>
+      </c>
+      <c r="H1480" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RKLB.xlsx
+++ b/data/RKLB.xlsx
@@ -38834,7 +38834,7 @@
         <v>46310.5625</v>
       </c>
       <c r="B1480" t="n">
-        <v>48106607</v>
+        <v>48563400</v>
       </c>
       <c r="C1480" t="n">
         <v>55.3979988098145</v>
@@ -38843,7 +38843,7 @@
         <v>49.693000793457</v>
       </c>
       <c r="E1480" t="n">
-        <v>54</v>
+        <v>53.8600006103516</v>
       </c>
       <c r="F1480" t="n">
         <v>55.25</v>
@@ -38852,6 +38852,32 @@
         <v>55.25</v>
       </c>
       <c r="H1480" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1481">
+      <c r="A1481" s="1" t="n">
+        <v>46311.5625</v>
+      </c>
+      <c r="B1481" t="n">
+        <v>23636672</v>
+      </c>
+      <c r="C1481" t="n">
+        <v>54.8549995422363</v>
+      </c>
+      <c r="D1481" t="n">
+        <v>50.3699989318848</v>
+      </c>
+      <c r="E1481" t="n">
+        <v>54.4900016784668</v>
+      </c>
+      <c r="F1481" t="n">
+        <v>50.8400001525879</v>
+      </c>
+      <c r="G1481" t="n">
+        <v>50.8400001525879</v>
+      </c>
+      <c r="H1481" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RKLB.xlsx
+++ b/data/RKLB.xlsx
@@ -43321,7 +43321,7 @@
         <v>50.8400001525879</v>
       </c>
       <c r="H1481" t="n">
-        <v>23869500</v>
+        <v>24048200</v>
       </c>
       <c r="I1481" t="s">
         <v>9</v>
@@ -43341,7 +43341,7 @@
         <v>52.9900016784668</v>
       </c>
       <c r="E1482" t="n">
-        <v>51.3101005554199</v>
+        <v>51.310001373291</v>
       </c>
       <c r="F1482" t="n">
         <v>51.3600006103516</v>
@@ -43350,9 +43350,38 @@
         <v>51.3600006103516</v>
       </c>
       <c r="H1482" t="n">
-        <v>16968066</v>
+        <v>17077100</v>
       </c>
       <c r="I1482" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1483">
+      <c r="A1483" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1483" s="1" t="n">
+        <v>46315.5625</v>
+      </c>
+      <c r="C1483" t="n">
+        <v>50.5349998474121</v>
+      </c>
+      <c r="D1483" t="n">
+        <v>52.7150001525879</v>
+      </c>
+      <c r="E1483" t="n">
+        <v>49.2500991821289</v>
+      </c>
+      <c r="F1483" t="n">
+        <v>50.9000015258789</v>
+      </c>
+      <c r="G1483" t="n">
+        <v>50.9000015258789</v>
+      </c>
+      <c r="H1483" t="n">
+        <v>16653261</v>
+      </c>
+      <c r="I1483" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RKLB.xlsx
+++ b/data/RKLB.xlsx
@@ -43364,13 +43364,13 @@
         <v>46315.5625</v>
       </c>
       <c r="C1483" t="n">
-        <v>50.5349998474121</v>
+        <v>50.564998626709</v>
       </c>
       <c r="D1483" t="n">
         <v>52.7150001525879</v>
       </c>
       <c r="E1483" t="n">
-        <v>49.2500991821289</v>
+        <v>49.25</v>
       </c>
       <c r="F1483" t="n">
         <v>50.9000015258789</v>
@@ -43379,9 +43379,38 @@
         <v>50.9000015258789</v>
       </c>
       <c r="H1483" t="n">
-        <v>16653261</v>
+        <v>16945200</v>
       </c>
       <c r="I1483" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1484">
+      <c r="A1484" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1484" s="1" t="n">
+        <v>46316.5625</v>
+      </c>
+      <c r="C1484" t="n">
+        <v>52.2099990844727</v>
+      </c>
+      <c r="D1484" t="n">
+        <v>53.8899993896484</v>
+      </c>
+      <c r="E1484" t="n">
+        <v>52.0200004577637</v>
+      </c>
+      <c r="F1484" t="n">
+        <v>53.6699981689453</v>
+      </c>
+      <c r="G1484" t="n">
+        <v>53.6699981689453</v>
+      </c>
+      <c r="H1484" t="n">
+        <v>17563720</v>
+      </c>
+      <c r="I1484" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RKLB.xlsx
+++ b/data/RKLB.xlsx
@@ -43393,10 +43393,10 @@
         <v>46316.5625</v>
       </c>
       <c r="C1484" t="n">
-        <v>52.2099990844727</v>
+        <v>52.2200012207031</v>
       </c>
       <c r="D1484" t="n">
-        <v>53.8899993896484</v>
+        <v>53.9000015258789</v>
       </c>
       <c r="E1484" t="n">
         <v>52.0200004577637</v>
@@ -43408,9 +43408,38 @@
         <v>53.6699981689453</v>
       </c>
       <c r="H1484" t="n">
-        <v>17563720</v>
+        <v>17857800</v>
       </c>
       <c r="I1484" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1485">
+      <c r="A1485" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1485" s="1" t="n">
+        <v>46317.5625</v>
+      </c>
+      <c r="C1485" t="n">
+        <v>51.6500015258789</v>
+      </c>
+      <c r="D1485" t="n">
+        <v>52.9799995422363</v>
+      </c>
+      <c r="E1485" t="n">
+        <v>49.9550018310547</v>
+      </c>
+      <c r="F1485" t="n">
+        <v>51.2200012207031</v>
+      </c>
+      <c r="G1485" t="n">
+        <v>51.2200012207031</v>
+      </c>
+      <c r="H1485" t="n">
+        <v>16555530</v>
+      </c>
+      <c r="I1485" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RKLB.xlsx
+++ b/data/RKLB.xlsx
@@ -43422,7 +43422,7 @@
         <v>46317.5625</v>
       </c>
       <c r="C1485" t="n">
-        <v>51.6500015258789</v>
+        <v>51.6749992370605</v>
       </c>
       <c r="D1485" t="n">
         <v>52.9799995422363</v>
@@ -43437,9 +43437,38 @@
         <v>51.2200012207031</v>
       </c>
       <c r="H1485" t="n">
-        <v>16555530</v>
+        <v>16674500</v>
       </c>
       <c r="I1485" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1486">
+      <c r="A1486" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1486" s="1" t="n">
+        <v>46318.5625</v>
+      </c>
+      <c r="C1486" t="n">
+        <v>50.7299995422363</v>
+      </c>
+      <c r="D1486" t="n">
+        <v>52.9150009155273</v>
+      </c>
+      <c r="E1486" t="n">
+        <v>49.5219993591309</v>
+      </c>
+      <c r="F1486" t="n">
+        <v>52.5999984741211</v>
+      </c>
+      <c r="G1486" t="n">
+        <v>52.5999984741211</v>
+      </c>
+      <c r="H1486" t="n">
+        <v>13364187</v>
+      </c>
+      <c r="I1486" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RKLB.xlsx
+++ b/data/RKLB.xlsx
@@ -43466,9 +43466,38 @@
         <v>52.5999984741211</v>
       </c>
       <c r="H1486" t="n">
-        <v>13364187</v>
+        <v>13391100</v>
       </c>
       <c r="I1486" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1487">
+      <c r="A1487" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1487" s="1" t="n">
+        <v>46321.5625</v>
+      </c>
+      <c r="C1487" t="n">
+        <v>52.5800018310547</v>
+      </c>
+      <c r="D1487" t="n">
+        <v>54.9900016784668</v>
+      </c>
+      <c r="E1487" t="n">
+        <v>52.1500015258789</v>
+      </c>
+      <c r="F1487" t="n">
+        <v>53.8199996948242</v>
+      </c>
+      <c r="G1487" t="n">
+        <v>53.8199996948242</v>
+      </c>
+      <c r="H1487" t="n">
+        <v>12573588</v>
+      </c>
+      <c r="I1487" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RKLB.xlsx
+++ b/data/RKLB.xlsx
@@ -43466,7 +43466,7 @@
         <v>52.5999984741211</v>
       </c>
       <c r="H1486" t="n">
-        <v>13391100</v>
+        <v>13443900</v>
       </c>
       <c r="I1486" t="s">
         <v>9</v>
@@ -43480,7 +43480,7 @@
         <v>46321.5625</v>
       </c>
       <c r="C1487" t="n">
-        <v>52.5800018310547</v>
+        <v>52.5999984741211</v>
       </c>
       <c r="D1487" t="n">
         <v>54.9900016784668</v>
@@ -43495,9 +43495,38 @@
         <v>53.8199996948242</v>
       </c>
       <c r="H1487" t="n">
-        <v>12573588</v>
+        <v>12671100</v>
       </c>
       <c r="I1487" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1488">
+      <c r="A1488" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1488" s="1" t="n">
+        <v>46322.5625</v>
+      </c>
+      <c r="C1488" t="n">
+        <v>54.0999984741211</v>
+      </c>
+      <c r="D1488" t="n">
+        <v>59.1799011230469</v>
+      </c>
+      <c r="E1488" t="n">
+        <v>53.5699996948242</v>
+      </c>
+      <c r="F1488" t="n">
+        <v>58.310001373291</v>
+      </c>
+      <c r="G1488" t="n">
+        <v>58.310001373291</v>
+      </c>
+      <c r="H1488" t="n">
+        <v>21203618</v>
+      </c>
+      <c r="I1488" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RKLB.xlsx
+++ b/data/RKLB.xlsx
@@ -43512,7 +43512,7 @@
         <v>54.0999984741211</v>
       </c>
       <c r="D1488" t="n">
-        <v>59.1799011230469</v>
+        <v>59.1800003051758</v>
       </c>
       <c r="E1488" t="n">
         <v>53.5699996948242</v>
@@ -43524,9 +43524,38 @@
         <v>58.310001373291</v>
       </c>
       <c r="H1488" t="n">
-        <v>21203618</v>
+        <v>21341400</v>
       </c>
       <c r="I1488" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1489">
+      <c r="A1489" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1489" s="1" t="n">
+        <v>46323.5625</v>
+      </c>
+      <c r="C1489" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="D1489" t="n">
+        <v>59.1287994384766</v>
+      </c>
+      <c r="E1489" t="n">
+        <v>56.939998626709</v>
+      </c>
+      <c r="F1489" t="n">
+        <v>58.5999984741211</v>
+      </c>
+      <c r="G1489" t="n">
+        <v>58.5999984741211</v>
+      </c>
+      <c r="H1489" t="n">
+        <v>12234830</v>
+      </c>
+      <c r="I1489" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RKLB.xlsx
+++ b/data/RKLB.xlsx
@@ -43538,10 +43538,10 @@
         <v>46323.5625</v>
       </c>
       <c r="C1489" t="n">
-        <v>58.5</v>
+        <v>58.4949989318848</v>
       </c>
       <c r="D1489" t="n">
-        <v>59.1287994384766</v>
+        <v>59.2999992370605</v>
       </c>
       <c r="E1489" t="n">
         <v>56.939998626709</v>
@@ -43553,9 +43553,38 @@
         <v>58.5999984741211</v>
       </c>
       <c r="H1489" t="n">
-        <v>12234830</v>
+        <v>12404100</v>
       </c>
       <c r="I1489" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1490">
+      <c r="A1490" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1490" s="1" t="n">
+        <v>46324.5625</v>
+      </c>
+      <c r="C1490" t="n">
+        <v>57.8400001525879</v>
+      </c>
+      <c r="D1490" t="n">
+        <v>61.1299018859863</v>
+      </c>
+      <c r="E1490" t="n">
+        <v>57.6324005126953</v>
+      </c>
+      <c r="F1490" t="n">
+        <v>59.0999984741211</v>
+      </c>
+      <c r="G1490" t="n">
+        <v>59.0999984741211</v>
+      </c>
+      <c r="H1490" t="n">
+        <v>14242221</v>
+      </c>
+      <c r="I1490" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RKLB.xlsx
+++ b/data/RKLB.xlsx
@@ -43567,13 +43567,13 @@
         <v>46324.5625</v>
       </c>
       <c r="C1490" t="n">
-        <v>57.8400001525879</v>
+        <v>57.7599983215332</v>
       </c>
       <c r="D1490" t="n">
-        <v>61.1299018859863</v>
+        <v>61.1300010681152</v>
       </c>
       <c r="E1490" t="n">
-        <v>57.6324005126953</v>
+        <v>57.6319999694824</v>
       </c>
       <c r="F1490" t="n">
         <v>59.0999984741211</v>
@@ -43582,9 +43582,38 @@
         <v>59.0999984741211</v>
       </c>
       <c r="H1490" t="n">
-        <v>14242221</v>
+        <v>14625800</v>
       </c>
       <c r="I1490" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1491">
+      <c r="A1491" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1491" s="1" t="n">
+        <v>46325.5625</v>
+      </c>
+      <c r="C1491" t="n">
+        <v>55.7099990844727</v>
+      </c>
+      <c r="D1491" t="n">
+        <v>57.5503997802734</v>
+      </c>
+      <c r="E1491" t="n">
+        <v>53.189998626709</v>
+      </c>
+      <c r="F1491" t="n">
+        <v>54.7299995422363</v>
+      </c>
+      <c r="G1491" t="n">
+        <v>54.7299995422363</v>
+      </c>
+      <c r="H1491" t="n">
+        <v>16454886</v>
+      </c>
+      <c r="I1491" t="s">
         <v>9</v>
       </c>
     </row>
